--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122544125</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>103021</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544193</v>
+        <v>122544388</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,34 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770999</v>
+        <v>771014</v>
       </c>
       <c r="R3" t="n">
-        <v>7111191</v>
+        <v>7111240</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544388</v>
+        <v>122544193</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,29 +912,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>771014</v>
+        <v>770999</v>
       </c>
       <c r="R4" t="n">
-        <v>7111240</v>
+        <v>7111191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544125</v>
+        <v>122544193</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770990</v>
+        <v>770999</v>
       </c>
       <c r="R2" t="n">
-        <v>7111194</v>
+        <v>7111191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544388</v>
+        <v>122544125</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,34 +802,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>771014</v>
+        <v>770990</v>
       </c>
       <c r="R3" t="n">
-        <v>7111240</v>
+        <v>7111194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544193</v>
+        <v>122544388</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,39 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770999</v>
+        <v>771014</v>
       </c>
       <c r="R4" t="n">
-        <v>7111191</v>
+        <v>7111240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544125</v>
+        <v>122544388</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,43 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770990</v>
+        <v>771014</v>
       </c>
       <c r="R3" t="n">
-        <v>7111194</v>
+        <v>7111240</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544388</v>
+        <v>122544125</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +908,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>771014</v>
+        <v>770990</v>
       </c>
       <c r="R4" t="n">
-        <v>7111240</v>
+        <v>7111194</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544193</v>
+        <v>122544388</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770999</v>
+        <v>771014</v>
       </c>
       <c r="R2" t="n">
-        <v>7111191</v>
+        <v>7111240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544388</v>
+        <v>122544193</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +797,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>771014</v>
+        <v>770999</v>
       </c>
       <c r="R3" t="n">
-        <v>7111240</v>
+        <v>7111191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544388</v>
+        <v>122544193</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>771014</v>
+        <v>770999</v>
       </c>
       <c r="R2" t="n">
-        <v>7111240</v>
+        <v>7111191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544193</v>
+        <v>122544125</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,27 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770999</v>
+        <v>770990</v>
       </c>
       <c r="R3" t="n">
-        <v>7111191</v>
+        <v>7111194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544125</v>
+        <v>122544388</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,43 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770990</v>
+        <v>771014</v>
       </c>
       <c r="R4" t="n">
-        <v>7111194</v>
+        <v>7111240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544193</v>
+        <v>122544125</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770999</v>
+        <v>770990</v>
       </c>
       <c r="R2" t="n">
-        <v>7111191</v>
+        <v>7111194</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544388</v>
+        <v>122544193</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +806,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>771014</v>
+        <v>770999</v>
       </c>
       <c r="R3" t="n">
-        <v>7111240</v>
+        <v>7111191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544125</v>
+        <v>122544388</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,43 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770990</v>
+        <v>771014</v>
       </c>
       <c r="R4" t="n">
-        <v>7111194</v>
+        <v>7111240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544125</v>
+        <v>122544193</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770990</v>
+        <v>770999</v>
       </c>
       <c r="R2" t="n">
-        <v>7111194</v>
+        <v>7111191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544193</v>
+        <v>122544388</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770999</v>
+        <v>771014</v>
       </c>
       <c r="R3" t="n">
-        <v>7111191</v>
+        <v>7111240</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544388</v>
+        <v>122544125</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +908,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>771014</v>
+        <v>770990</v>
       </c>
       <c r="R4" t="n">
-        <v>7111240</v>
+        <v>7111194</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544193</v>
+        <v>122544388</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>78762</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770999</v>
+        <v>771014</v>
       </c>
       <c r="R2" t="n">
-        <v>7111191</v>
+        <v>7111240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544388</v>
+        <v>122544193</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +797,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>771014</v>
+        <v>770999</v>
       </c>
       <c r="R3" t="n">
-        <v>7111240</v>
+        <v>7111191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +895,7 @@
         <v>122544125</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544388</v>
+        <v>122544193</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>771014</v>
+        <v>770999</v>
       </c>
       <c r="R2" t="n">
-        <v>7111240</v>
+        <v>7111191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544193</v>
+        <v>122544388</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770999</v>
+        <v>771014</v>
       </c>
       <c r="R3" t="n">
-        <v>7111191</v>
+        <v>7111240</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544193</v>
+        <v>122544125</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770999</v>
+        <v>770990</v>
       </c>
       <c r="R2" t="n">
-        <v>7111191</v>
+        <v>7111194</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544388</v>
+        <v>122544193</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +806,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>771014</v>
+        <v>770999</v>
       </c>
       <c r="R3" t="n">
-        <v>7111240</v>
+        <v>7111191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544125</v>
+        <v>122544388</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,43 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770990</v>
+        <v>771014</v>
       </c>
       <c r="R4" t="n">
-        <v>7111194</v>
+        <v>7111240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544125</v>
+        <v>122544193</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770990</v>
+        <v>770999</v>
       </c>
       <c r="R2" t="n">
-        <v>7111194</v>
+        <v>7111191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544193</v>
+        <v>122544125</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,27 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770999</v>
+        <v>770990</v>
       </c>
       <c r="R3" t="n">
-        <v>7111191</v>
+        <v>7111194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 39861-2024 artfynd.xlsx
+++ b/artfynd/A 39861-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544193</v>
+        <v>122544388</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770999</v>
+        <v>771014</v>
       </c>
       <c r="R2" t="n">
-        <v>7111191</v>
+        <v>7111240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -901,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544388</v>
+        <v>122544193</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +912,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>771014</v>
+        <v>770999</v>
       </c>
       <c r="R4" t="n">
-        <v>7111240</v>
+        <v>7111191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
